--- a/data.xlsx
+++ b/data.xlsx
@@ -1,43 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\Whatsapp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\Whatsapp_Final\wa_blast_gatsu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18A0E57-B4A1-489B-ABEC-4FC0F80FA513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229F3DF1-8860-46BE-AD7E-9D9435937417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>CIF</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Nama</t>
   </si>
@@ -45,12 +28,6 @@
     <t>NoHP</t>
   </si>
   <si>
-    <t>message</t>
-  </si>
-  <si>
-    <t>link wa</t>
-  </si>
-  <si>
     <t>arya</t>
   </si>
   <si>
@@ -70,13 +47,22 @@
   </si>
   <si>
     <t>6285376996538</t>
+  </si>
+  <si>
+    <t>Perusahaan</t>
+  </si>
+  <si>
+    <t>PT Best</t>
+  </si>
+  <si>
+    <t>Mandiri</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,14 +78,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -109,7 +87,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -132,42 +110,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -184,9 +143,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -224,9 +183,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -259,26 +218,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -311,26 +253,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -504,80 +429,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>393</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="4" t="str">
-        <f>HYPERLINK("https://wa.me/" &amp; D2)</f>
-        <v>https://wa.me/6285723520040</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>394</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="str">
-        <f t="shared" ref="E3" si="0">HYPERLINK("https://wa.me/" &amp; D3)</f>
-        <v>https://wa.me/6285376996538</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\Whatsapp_Final\wa_blast_gatsu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229F3DF1-8860-46BE-AD7E-9D9435937417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B481F79F-6EF9-43AA-8DE0-C8BF7E2FFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\Whatsapp_Final\wa_blast_gatsu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B481F79F-6EF9-43AA-8DE0-C8BF7E2FFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61FF00F-0B35-45A4-A135-2BB4262744BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>Laki-laki</t>
   </si>
   <si>
-    <t>Jenis Kelamin</t>
-  </si>
-  <si>
     <t>6285723520040</t>
   </si>
   <si>
@@ -56,6 +53,9 @@
   </si>
   <si>
     <t>Mandiri</t>
+  </si>
+  <si>
+    <t>Gender</t>
   </si>
 </sst>
 </file>
@@ -445,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -470,13 +470,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
